--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -767,13 +767,13 @@
         <v>490</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1228.49</v>
+        <v>1494.54</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>133.891</v>
+        <v>79.6344</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>0.108988</v>
+        <v>0.0532835</v>
       </c>
       <c r="L6" s="10" t="n">
         <v>2</v>
@@ -782,7 +782,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>longest of 2 measurements; measurements scatter by 11%, above the 10% threshold — needs a decision, not a rule; rejected 4_ACN_Ar_200ns_-5M_3mL_IrdFppy: window spans 3.6 lifetimes, below the 5 required; rejected 4_ACN_Ar_20us_-5M_3mL_IrdFppy: duplicate of 4_ACN_Ar_10us_-5M_3mL_IrdFppy</t>
+          <t>longest of 2 measurements; rejected 4_ACN_Ar_200ns_-5M_3mL_IrdFppy: not fitted; rejected 4_ACN_Ar_20us_-5M_3mL_IrdFppy: duplicate of 4_ACN_Ar_10us_-5M_3mL_IrdFppy</t>
         </is>
       </c>
     </row>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,7 @@
     <col width="2" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="45" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -515,11 +510,6 @@
       </c>
       <c r="J1" s="6" t="n"/>
       <c r="K1" s="6" t="n"/>
-      <c r="L1" s="6" t="n"/>
-      <c r="M1" s="6" t="n"/>
-      <c r="N1" s="6" t="n"/>
-      <c r="O1" s="6" t="n"/>
-      <c r="P1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -559,35 +549,10 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>tau0_std / ns</t>
+          <t>tau0_err / ns</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
-        <is>
-          <t>tau0_rsd</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="inlineStr">
-        <is>
-          <t>n_measurements</t>
-        </is>
-      </c>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>n_traces_rejected</t>
-        </is>
-      </c>
-      <c r="N2" s="9" t="inlineStr">
-        <is>
-          <t>tau0_consistent</t>
-        </is>
-      </c>
-      <c r="O2" s="9" t="inlineStr">
-        <is>
-          <t>trace_used</t>
-        </is>
-      </c>
-      <c r="P2" s="9" t="inlineStr">
         <is>
           <t>tau0_note</t>
         </is>
@@ -622,26 +587,7 @@
       <c r="J3" s="10" t="n">
         <v>5.30814</v>
       </c>
-      <c r="K3" s="10" t="n">
-        <v>0.00222302</v>
-      </c>
-      <c r="L3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>1_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
@@ -672,26 +618,7 @@
       <c r="J4" s="10" t="n">
         <v>1.70003</v>
       </c>
-      <c r="K4" s="10" t="n">
-        <v>0.00305149</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="inlineStr">
-        <is>
-          <t>2_ACN_Ar_10us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n">
@@ -722,26 +649,7 @@
       <c r="J5" s="10" t="n">
         <v>4.13219</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>0.00243308</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>3_ACN_Ar_10us_-5M_3mL_Irppy</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error; rejected 3_ACN_Ar_20us_-5M_3mL_Irppy: duplicate of 3_ACN_Ar_10us_-5M_3mL_Irppy</t>
-        </is>
-      </c>
+      <c r="K5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -770,28 +678,11 @@
         <v>1494.54</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>79.6344</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>0.0532835</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>4_ACN_Ar_10us_-5M_3mL_IrdFppy</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="inlineStr">
-        <is>
-          <t>longest of 2 measurements; rejected 4_ACN_Ar_200ns_-5M_3mL_IrdFppy: not fitted; rejected 4_ACN_Ar_20us_-5M_3mL_IrdFppy: duplicate of 4_ACN_Ar_10us_-5M_3mL_IrdFppy</t>
+        <v>19.3165</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>fit start fixed at 1500 ns</t>
         </is>
       </c>
     </row>
@@ -824,26 +715,7 @@
       <c r="J7" s="10" t="n">
         <v>2.1878</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0.00250407</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10" t="n"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>5_ACN_Ar_10us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -874,26 +746,7 @@
       <c r="J8" s="10" t="n">
         <v>1.82806</v>
       </c>
-      <c r="K8" s="10" t="n">
-        <v>0.00291845</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>6_ACN_Ar_10us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P8" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -914,32 +767,9 @@
       </c>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
-      <c r="I9" s="10" t="n">
-        <v>0.255827</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.00118839</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.00464529</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10" t="n"/>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>7_ACN_Ar_10ns_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -970,26 +800,7 @@
       <c r="J10" s="10" t="n">
         <v>14.9412</v>
       </c>
-      <c r="K10" s="10" t="n">
-        <v>0.00232049</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>8_ACN_Ar_50us_-5M_3mL_IrCF3pmb</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -1020,26 +831,7 @@
       <c r="J11" s="10" t="n">
         <v>4.73231</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0.00204433</v>
-      </c>
-      <c r="L11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10" t="n"/>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>9_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -1070,26 +862,7 @@
       <c r="J12" s="10" t="n">
         <v>0.206387</v>
       </c>
-      <c r="K12" s="10" t="n">
-        <v>0.00276451</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="10" t="n"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>10_ACN_Ar_1us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -1120,26 +893,7 @@
       <c r="J13" s="10" t="n">
         <v>3.82431</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0.00287235</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>11_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -1170,26 +924,7 @@
       <c r="J14" s="10" t="n">
         <v>3.903</v>
       </c>
-      <c r="K14" s="10" t="n">
-        <v>0.0027297</v>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="10" t="n"/>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>12_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P14" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -1220,26 +955,7 @@
       <c r="J15" s="10" t="n">
         <v>5.07795</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>0.0021741</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10" t="n"/>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>13_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -1270,26 +986,7 @@
       <c r="J16" s="10" t="n">
         <v>4.93813</v>
       </c>
-      <c r="K16" s="10" t="n">
-        <v>0.00211888</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10" t="n"/>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>14_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P16" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -1318,30 +1015,9 @@
         <v>3417.56</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>119.027</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <v>0.0348281</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>15_ACN_Ar_50us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="inlineStr">
-        <is>
-          <t>longest of 2 measurements</t>
-        </is>
-      </c>
+        <v>9.249000000000001</v>
+      </c>
+      <c r="K17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -1372,26 +1048,7 @@
       <c r="J18" s="10" t="n">
         <v>4.11826</v>
       </c>
-      <c r="K18" s="10" t="n">
-        <v>0.00267426</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>16_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -1422,26 +1079,7 @@
       <c r="J19" s="10" t="n">
         <v>0.916385</v>
       </c>
-      <c r="K19" s="10" t="n">
-        <v>0.00330365</v>
-      </c>
-      <c r="L19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>17_ACN_Ar_5us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -1472,26 +1110,7 @@
       <c r="J20" s="10" t="n">
         <v>9.456340000000001</v>
       </c>
-      <c r="K20" s="10" t="n">
-        <v>0.00258048</v>
-      </c>
-      <c r="L20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="inlineStr">
-        <is>
-          <t>18_ACN_Ar_50us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P20" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -1522,26 +1141,7 @@
       <c r="J21" s="10" t="n">
         <v>13.4651</v>
       </c>
-      <c r="K21" s="10" t="n">
-        <v>0.00283127</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10" t="inlineStr">
-        <is>
-          <t>19_ACN_Ar_50us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -1572,26 +1172,7 @@
       <c r="J22" s="10" t="n">
         <v>4.09436</v>
       </c>
-      <c r="K22" s="10" t="n">
-        <v>0.00269511</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="10" t="n"/>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>20_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P22" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -1622,26 +1203,7 @@
       <c r="J23" s="10" t="n">
         <v>4.45561</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>0.00222854</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="10" t="n"/>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>21_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -1670,30 +1232,9 @@
         <v>3304.66</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>111.136</v>
-      </c>
-      <c r="K24" s="10" t="n">
-        <v>0.03363</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
-        <is>
-          <t>22_ACN_Ar_50us_-5M_3mL_betterDegas</t>
-        </is>
-      </c>
-      <c r="P24" s="10" t="inlineStr">
-        <is>
-          <t>longest of 3 measurements</t>
-        </is>
-      </c>
+        <v>9.446070000000001</v>
+      </c>
+      <c r="K24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -1724,26 +1265,7 @@
       <c r="J25" s="10" t="n">
         <v>10.683</v>
       </c>
-      <c r="K25" s="10" t="n">
-        <v>0.00238048</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="10" t="n"/>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>23_ACN_Ar_50us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -1774,26 +1296,7 @@
       <c r="J26" s="10" t="n">
         <v>7.49855</v>
       </c>
-      <c r="K26" s="10" t="n">
-        <v>0.00561984</v>
-      </c>
-      <c r="L26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="10" t="n"/>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>24_ACN_Ar_10us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P26" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error; rejected 24_ACN_Ar_10ns_-5M_3mL: not fitted</t>
-        </is>
-      </c>
+      <c r="K26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -1824,26 +1327,7 @@
       <c r="J27" s="10" t="n">
         <v>3.76114</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0.00286086</v>
-      </c>
-      <c r="L27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10" t="inlineStr">
-        <is>
-          <t>25_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P27" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -1863,11 +1347,6 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="10" t="n"/>
       <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
-      <c r="M28" s="10" t="n"/>
-      <c r="N28" s="10" t="n"/>
-      <c r="O28" s="10" t="n"/>
-      <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -1898,26 +1377,7 @@
       <c r="J29" s="10" t="n">
         <v>2.06671</v>
       </c>
-      <c r="K29" s="10" t="n">
-        <v>0.00270585</v>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="10" t="n"/>
-      <c r="O29" s="10" t="inlineStr">
-        <is>
-          <t>27_ACN_Ar_10us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P29" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -1948,26 +1408,7 @@
       <c r="J30" s="10" t="n">
         <v>8.609540000000001</v>
       </c>
-      <c r="K30" s="10" t="n">
-        <v>0.00315807</v>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="10" t="n"/>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>28_ACN_Ar_50us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P30" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -1998,32 +1439,13 @@
       <c r="J31" s="10" t="n">
         <v>4.24662</v>
       </c>
-      <c r="K31" s="10" t="n">
-        <v>0.00262042</v>
-      </c>
-      <c r="L31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>29_ACN_Ar_20us_-5M_3mL</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
-        <is>
-          <t>single measurement, within-fit standard error</t>
-        </is>
-      </c>
+      <c r="K31" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="I1:P1"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2035,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2236,12 +1658,12 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Unquenched lifetime: the longest of the usable measurements, because residual oxygen can only shorten it.</t>
+          <t>Unquenched lifetime, single-exponential fit of pc_tcspc/PC&lt;n&gt;.txt.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: tau0_ns</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_ns</t>
         </is>
       </c>
     </row>
@@ -2253,7 +1675,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>tau0_std / ns</t>
+          <t>tau0_err / ns</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -2263,12 +1685,12 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Spread across repeats; with one measurement, that fit's standard error.</t>
+          <t>Standard error of that fit.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: tau0_std_ns</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_err_ns</t>
         </is>
       </c>
     </row>
@@ -2280,186 +1702,71 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>tau0_rsd</t>
+          <t>tau0_note</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>tau0_std / tau0.</t>
+          <t>Deviation from the standard fit window.</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: tau0_rsd</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: note</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>n_measurements</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Usable traces behind tau0.</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: n_measurements</t>
-        </is>
-      </c>
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>n_traces_rejected</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Traces dropped as duplicates, unfitted, or with too short a window.</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: n_traces_rejected</t>
-        </is>
-      </c>
+          <t>One row per photocatalyst with a compound record. PC7 and PC26 are not in the screen</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>tau0_consistent</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>With repeats: 1 if they agree within 10 %, 0 if not. Blank for one measurement.</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: consistent</t>
-        </is>
-      </c>
+          <t>and have no lifetime. PC24 is in the screen and excluded from the dataset in</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>trace_used</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>The trace tau0 is taken from.</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: trace_used</t>
-        </is>
-      </c>
+          <t>dataset/build_dataset.py, not here.</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>tau0_note</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>How tau0 was selected, and what was rejected.</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tau0.csv: note</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>One row per photocatalyst with a compound record. PC7 was measured but is not in the</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>screen; PC26 has no record beyond its number. PC24 is in the screen and excluded from</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>the dataset in dataset/build_dataset.py, not here.</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
           <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -1749,7 +1749,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>dataset/build_dataset.py, not here.</t>
+          <t>data/build_exp_dataset.py, not here.</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -472,20 +472,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="2" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="2" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -502,24 +501,23 @@
         </is>
       </c>
       <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
         </is>
       </c>
+      <c r="I1" s="6" t="n"/>
       <c r="J1" s="6" t="n"/>
-      <c r="K1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>pc_id</t>
+          <t>new_id</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>pc_name</t>
+          <t>old_id</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -529,30 +527,25 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>in_screen</t>
+          <t>excitation / nm</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>excitation / nm</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
           <t>emission / nm</t>
         </is>
       </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>tau0 / ns</t>
+        </is>
+      </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>tau0 / ns</t>
+          <t>tau0_err / ns</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>tau0_err / ns</t>
-        </is>
-      </c>
-      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>tau0_note</t>
         </is>
@@ -562,10 +555,8 @@
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>PC1</t>
-        </is>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
@@ -573,30 +564,25 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G3" s="10" t="n">
         <v>475</v>
       </c>
+      <c r="H3" s="10" t="n">
+        <v>2387.81</v>
+      </c>
       <c r="I3" s="10" t="n">
-        <v>2387.81</v>
-      </c>
-      <c r="J3" s="10" t="n">
         <v>5.30814</v>
       </c>
-      <c r="K3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>PC2</t>
-        </is>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
@@ -604,30 +590,25 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G4" s="10" t="n">
         <v>580</v>
       </c>
+      <c r="H4" s="10" t="n">
+        <v>557.115</v>
+      </c>
       <c r="I4" s="10" t="n">
-        <v>557.115</v>
-      </c>
-      <c r="J4" s="10" t="n">
         <v>1.70003</v>
       </c>
-      <c r="K4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
+      <c r="B5" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
@@ -635,30 +616,25 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G5" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="H5" s="10" t="n">
+        <v>1698.34</v>
+      </c>
       <c r="I5" s="10" t="n">
-        <v>1698.34</v>
-      </c>
-      <c r="J5" s="10" t="n">
         <v>4.13219</v>
       </c>
-      <c r="K5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
+      <c r="B6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
@@ -666,21 +642,18 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G6" s="10" t="n">
         <v>490</v>
       </c>
+      <c r="H6" s="10" t="n">
+        <v>1494.54</v>
+      </c>
       <c r="I6" s="10" t="n">
-        <v>1494.54</v>
-      </c>
-      <c r="J6" s="10" t="n">
         <v>19.3165</v>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>fit start fixed at 1500 ns</t>
         </is>
@@ -690,10 +663,8 @@
       <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
+      <c r="B7" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
@@ -701,30 +672,25 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="G7" s="10" t="n">
         <v>625</v>
       </c>
+      <c r="H7" s="10" t="n">
+        <v>873.699</v>
+      </c>
       <c r="I7" s="10" t="n">
-        <v>873.699</v>
-      </c>
-      <c r="J7" s="10" t="n">
         <v>2.1878</v>
       </c>
-      <c r="K7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>PC6</t>
-        </is>
+      <c r="B8" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -732,720 +698,570 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="G8" s="10" t="n">
         <v>600</v>
       </c>
+      <c r="H8" s="10" t="n">
+        <v>626.38</v>
+      </c>
       <c r="I8" s="10" t="n">
-        <v>626.38</v>
-      </c>
-      <c r="J8" s="10" t="n">
         <v>1.82806</v>
       </c>
-      <c r="K8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>PC7</t>
-        </is>
+      <c r="B9" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>iPrTXT</t>
+          <t>Ir(dF(Me)ppy)3</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="I9" s="10" t="n"/>
+        <v>425</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>475</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>2314.85</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>4.73231</v>
+      </c>
       <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>PC8</t>
-        </is>
+      <c r="B10" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>[Ir(CF3-pmb)3]</t>
+          <t>[Ir(dF(CF3)ppy)2(d(5,5)CF3bpy)]PF6</t>
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>380</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>415</v>
+        <v>645</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>74.6559</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>6438.81</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>14.9412</v>
-      </c>
-      <c r="K10" s="10" t="n"/>
+        <v>0.206387</v>
+      </c>
+      <c r="J10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>PC9</t>
-        </is>
+      <c r="B11" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Ir(dF(Me)ppy)3</t>
+          <t>[Ir(dFppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>475</v>
+        <v>510</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>1331.42</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2314.85</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>4.73231</v>
-      </c>
-      <c r="K11" s="10" t="n"/>
+        <v>3.82431</v>
+      </c>
+      <c r="J11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>PC10</t>
-        </is>
+      <c r="B12" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(CF3)ppy)2(d(5,5)CF3bpy)]PF6</t>
+          <t>[Ir(dF(Me)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>645</v>
+        <v>520</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>1429.83</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>74.6559</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>0.206387</v>
-      </c>
-      <c r="K12" s="10" t="n"/>
+        <v>3.903</v>
+      </c>
+      <c r="J12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>PC11</t>
-        </is>
+      <c r="B13" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dFppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(dF(CF3)ppy)2(bpy)]PF6</t>
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>510</v>
+        <v>475</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>2335.66</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1331.42</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>3.82431</v>
-      </c>
-      <c r="K13" s="10" t="n"/>
+        <v>5.07795</v>
+      </c>
+      <c r="J13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>PC12</t>
-        </is>
+      <c r="B14" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(Me)ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(dF(Me)ppy)2(d(5,5)CH3bpy)]PF6</t>
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>520</v>
+        <v>500</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>2330.54</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1429.83</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>3.903</v>
-      </c>
-      <c r="K14" s="10" t="n"/>
+        <v>4.93813</v>
+      </c>
+      <c r="J14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>PC13</t>
-        </is>
+      <c r="B15" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(CF3)ppy)2(bpy)]PF6</t>
+          <t>[Ir(tCF3ppy)2(d(5,5)CH3bpy)]PF6</t>
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>475</v>
+        <v>520</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>3417.56</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>2335.66</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>5.07795</v>
-      </c>
-      <c r="K15" s="10" t="n"/>
+        <v>9.249000000000001</v>
+      </c>
+      <c r="J15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>PC14</t>
-        </is>
+      <c r="B16" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(Me)ppy)2(d(5,5)CH3bpy)]PF6</t>
+          <t>[Ir(dF(Me)ppy)2(d(OMe)bpy)]PF6</t>
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>500</v>
+        <v>520</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>1539.96</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2330.54</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>4.93813</v>
-      </c>
-      <c r="K16" s="10" t="n"/>
+        <v>4.11826</v>
+      </c>
+      <c r="J16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>PC15</t>
-        </is>
+      <c r="B17" s="10" t="n">
+        <v>17</v>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>[Ir(tCF3ppy)2(d(5,5)CH3bpy)]PF6</t>
+          <t>[Ir(ppy)2(d(OMe)bpy)]PF6</t>
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>520</v>
+        <v>580</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>277.386</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>3417.56</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>9.249000000000001</v>
-      </c>
-      <c r="K17" s="10" t="n"/>
+        <v>0.916385</v>
+      </c>
+      <c r="J17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>PC16</t>
-        </is>
+      <c r="B18" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(Me)ppy)2(d(OMe)bpy)]PF6</t>
+          <t>[Ir(tCF3ppy)2(d(5,5)OMebpy)]PF6</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G18" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="H18" s="10" t="n">
+        <v>3664.57</v>
+      </c>
       <c r="I18" s="10" t="n">
-        <v>1539.96</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>4.11826</v>
-      </c>
-      <c r="K18" s="10" t="n"/>
+        <v>9.456340000000001</v>
+      </c>
+      <c r="J18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>PC17</t>
-        </is>
+      <c r="B19" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>[Ir(ppy)2(d(OMe)bpy)]PF6</t>
+          <t>[Ir(dCF3ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>580</v>
+        <v>500</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>4755.86</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>277.386</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>0.916385</v>
-      </c>
-      <c r="K19" s="10" t="n"/>
+        <v>13.4651</v>
+      </c>
+      <c r="J19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>PC18</t>
-        </is>
+      <c r="B20" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>[Ir(tCF3ppy)2(d(5,5)OMebpy)]PF6</t>
+          <t>[Ir(dF(6-OMe)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>520</v>
+        <v>495</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>1519.18</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>3664.57</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>9.456340000000001</v>
-      </c>
-      <c r="K20" s="10" t="n"/>
+        <v>4.09436</v>
+      </c>
+      <c r="J20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>PC19</t>
-        </is>
+      <c r="B21" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dCF3ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(dF(OMe)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>500</v>
+        <v>520</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>1999.34</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>4755.86</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>13.4651</v>
-      </c>
-      <c r="K21" s="10" t="n"/>
+        <v>4.45561</v>
+      </c>
+      <c r="J21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>PC20</t>
-        </is>
+      <c r="B22" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(6-OMe)ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(tCF3ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>405</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>495</v>
+        <v>520</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>3304.66</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1519.18</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>4.09436</v>
-      </c>
-      <c r="K22" s="10" t="n"/>
+        <v>9.446070000000001</v>
+      </c>
+      <c r="J22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>PC21</t>
-        </is>
+      <c r="B23" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(OMe)ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(tetraFppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>520</v>
+        <v>490</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>4487.75</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1999.34</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>4.45561</v>
-      </c>
-      <c r="K23" s="10" t="n"/>
+        <v>10.683</v>
+      </c>
+      <c r="J23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>PC22</t>
-        </is>
+      <c r="B24" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>[Ir(tCF3ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(d(OMe)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>520</v>
+        <v>490</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>1334.3</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>3304.66</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>9.446070000000001</v>
-      </c>
-      <c r="K24" s="10" t="n"/>
+        <v>7.49855</v>
+      </c>
+      <c r="J24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>PC23</t>
-        </is>
+      <c r="B25" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>[Ir(tetraFppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(dF(4-Me)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>405</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>490</v>
+        <v>520</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>1314.69</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>4487.75</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>10.683</v>
-      </c>
-      <c r="K25" s="10" t="n"/>
+        <v>3.76114</v>
+      </c>
+      <c r="J25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>PC24</t>
-        </is>
+      <c r="B26" s="10" t="n">
+        <v>27</v>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>[Ir(d(OMe)ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(ppy)2(phen)]PF6</t>
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>490</v>
+        <v>590</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>763.793</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1334.3</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>7.49855</v>
-      </c>
-      <c r="K26" s="10" t="n"/>
+        <v>2.06671</v>
+      </c>
+      <c r="J26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>PC25</t>
-        </is>
+      <c r="B27" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>[Ir(dF(4-Me)ppy)2(dtbbpy)]PF6</t>
+          <t>[Ir(CF3-pmb)3]</t>
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>520</v>
+        <v>415</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>6438.81</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1314.69</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>3.76114</v>
-      </c>
-      <c r="K27" s="10" t="n"/>
+        <v>14.9412</v>
+      </c>
+      <c r="J27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>PC26</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="n"/>
+      <c r="B28" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>[Ir(CH3-pmb)3]</t>
+        </is>
+      </c>
       <c r="E28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
+        <v>380</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>415</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>2726.2</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>8.609540000000001</v>
+      </c>
       <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>PC27</t>
-        </is>
+      <c r="B29" s="10" t="n">
+        <v>29</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>[Ir(ppy)2(phen)]PF6</t>
+          <t>[Ir(pmb)3]</t>
         </is>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>590</v>
+        <v>415</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>1620.59</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>763.793</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>2.06671</v>
-      </c>
-      <c r="K29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>PC28</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>[Ir(CH3-pmb)3]</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>380</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>415</v>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>2726.2</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>8.609540000000001</v>
-      </c>
-      <c r="K30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>PC29</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>[Ir(pmb)3]</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>380</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>415</v>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>1620.59</v>
-      </c>
-      <c r="J31" s="10" t="n">
         <v>4.24662</v>
       </c>
-      <c r="K31" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1457,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1502,18 +1318,18 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>pc_id</t>
+          <t>new_id</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr"/>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Photocatalyst number.</t>
+          <t>PC number used downstream and in the paper, 1-27.</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: pc_id</t>
+          <t>photocatalyst_ids.py</t>
         </is>
       </c>
     </row>
@@ -1525,18 +1341,18 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>pc_name</t>
+          <t>old_id</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr"/>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Label used throughout, PC&lt;n&gt;.</t>
+          <t>PC number during the screen, used by the raw files.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: pc_name</t>
+          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: pc_id</t>
         </is>
       </c>
     </row>
@@ -1571,18 +1387,22 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>in_screen</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr"/>
+          <t>excitation / nm</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>1 if the photocatalyst has Stern-Volmer fits against the quencher set, 0 if not.</t>
+          <t>Excitation wavelength used in the screen.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_processed/stern_volmer_fits.csv: pc_id</t>
+          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: excitation_nm</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1414,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>excitation / nm</t>
+          <t>emission / nm</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1604,39 +1424,39 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Excitation wavelength used in the screen.</t>
+          <t>Emission wavelength read in the screen.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: excitation_nm</t>
+          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: emission_nm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Stern-Volmer screen</t>
+          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>emission / nm</t>
+          <t>tau0 / ns</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Emission wavelength read in the screen.</t>
+          <t>Unquenched lifetime, single-exponential fit of pc_tcspc/PC&lt;n&gt;.txt.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: emission_nm</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_ns</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1468,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>tau0 / ns</t>
+          <t>tau0_err / ns</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1658,12 +1478,12 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Unquenched lifetime, single-exponential fit of pc_tcspc/PC&lt;n&gt;.txt.</t>
+          <t>Standard error of that fit.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_ns</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_err_ns</t>
         </is>
       </c>
     </row>
@@ -1675,50 +1495,34 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>tau0_err / ns</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
+          <t>tau0_note</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr"/>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Standard error of that fit.</t>
+          <t>Deviation from the standard fit window.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_err_ns</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: note</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>tau0_note</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Deviation from the standard fit window.</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: note</t>
-        </is>
-      </c>
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>One row per photocatalyst in the screen, sorted by new_id. The raw files use old_id;</t>
+        </is>
+      </c>
       <c r="B11" s="12" t="n"/>
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="13" t="n"/>
@@ -1727,7 +1531,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>One row per photocatalyst with a compound record. PC7 and PC26 are not in the screen</t>
+          <t>the mapping is data/photocatalyst_ids.py. new_id 22 (old 24) is kept here and dropped</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -1738,7 +1542,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>and have no lifetime. PC24 is in the screen and excluded from the dataset in</t>
+          <t>by the theory benchmark: its emission was too weak.</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -1749,7 +1553,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>data/build_exp_dataset.py, not here.</t>
+          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -1757,17 +1561,6 @@
       <c r="D14" s="13" t="n"/>
       <c r="E14" s="12" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>74.6559</v>
@@ -805,7 +805,7 @@
         <v>425</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>1429.83</v>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>520</v>
@@ -1091,7 +1091,7 @@
         <v>405</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>4487.75</v>
@@ -1169,7 +1169,7 @@
         <v>425</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>763.793</v>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Excitation wavelength used in the screen.</t>
+          <t>Excitation filter centre in the Stern-Volmer screen, from the plate export (old PC1 and PC3: from the photocatalyst sheet).</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: excitation_nm</t>
+          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: excitation_nm</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Emission wavelength read in the screen.</t>
+          <t>Emission filter centre in the Stern-Volmer screen, from the plate export (old PC1 and PC3: from the photocatalyst sheet).</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: emission_nm</t>
+          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: emission_nm</t>
         </is>
       </c>
     </row>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>photocatalyst_ids.py</t>
+          <t>compound_identification.xlsx: Photocatalysts/new_id</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: pc_id</t>
+          <t>compound_identification.xlsx: Photocatalysts/old_id</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       <c r="C4" s="12" t="inlineStr"/>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Compound, as recorded.</t>
+          <t>Compound.</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/compound_records/compound_records_photocatalysts.csv: name</t>
+          <t>compound_identification.xlsx: Photocatalysts/name</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>the mapping is data/photocatalyst_ids.py. new_id 22 (old 24) is kept here and dropped</t>
+          <t>the mapping is data/compound_identification.xlsx. new_id 22 (old 24) is kept here and dropped</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -472,19 +472,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="2" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -494,20 +493,19 @@
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Stern-Volmer screen</t>
         </is>
       </c>
-      <c r="F1" s="4" t="n"/>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="n"/>
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
         </is>
       </c>
+      <c r="H1" s="6" t="n"/>
       <c r="I1" s="6" t="n"/>
-      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -517,35 +515,30 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>old_id</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
           <t>compound</t>
         </is>
       </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>excitation / nm</t>
+        </is>
+      </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>excitation / nm</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
           <t>emission / nm</t>
         </is>
       </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>tau0 / ns</t>
+        </is>
+      </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>tau0 / ns</t>
+          <t>tau0_err / ns</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>tau0_err / ns</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>tau0_note</t>
         </is>
@@ -555,105 +548,93 @@
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(CF3)ppy)2(dtbbpy)][PF6]</t>
         </is>
       </c>
+      <c r="D3" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E3" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F3" s="10" t="n">
         <v>475</v>
       </c>
+      <c r="G3" s="10" t="n">
+        <v>2387.81</v>
+      </c>
       <c r="H3" s="10" t="n">
-        <v>2387.81</v>
-      </c>
-      <c r="I3" s="10" t="n">
         <v>5.30814</v>
       </c>
-      <c r="J3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>[Ir(ppy)2(dtbbpy)][PF6]</t>
         </is>
       </c>
+      <c r="D4" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E4" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F4" s="10" t="n">
         <v>580</v>
       </c>
+      <c r="G4" s="10" t="n">
+        <v>557.115</v>
+      </c>
       <c r="H4" s="10" t="n">
-        <v>557.115</v>
-      </c>
-      <c r="I4" s="10" t="n">
         <v>1.70003</v>
       </c>
-      <c r="J4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Ir(ppy)3</t>
         </is>
       </c>
+      <c r="D5" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E5" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F5" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G5" s="10" t="n">
+        <v>1698.34</v>
+      </c>
       <c r="H5" s="10" t="n">
-        <v>1698.34</v>
-      </c>
-      <c r="I5" s="10" t="n">
         <v>4.13219</v>
       </c>
-      <c r="J5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Ir(dFppy)3</t>
         </is>
       </c>
+      <c r="D6" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E6" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F6" s="10" t="n">
         <v>490</v>
       </c>
+      <c r="G6" s="10" t="n">
+        <v>1494.54</v>
+      </c>
       <c r="H6" s="10" t="n">
-        <v>1494.54</v>
-      </c>
-      <c r="I6" s="10" t="n">
         <v>19.3165</v>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>fit start fixed at 1500 ns</t>
         </is>
@@ -663,605 +644,536 @@
       <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>[Ru(dtbbpy)3][PF6]2</t>
         </is>
       </c>
+      <c r="D7" s="10" t="n">
+        <v>450</v>
+      </c>
       <c r="E7" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="F7" s="10" t="n">
         <v>625</v>
       </c>
+      <c r="G7" s="10" t="n">
+        <v>873.699</v>
+      </c>
       <c r="H7" s="10" t="n">
-        <v>873.699</v>
-      </c>
-      <c r="I7" s="10" t="n">
         <v>2.1878</v>
       </c>
-      <c r="J7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>[Ru(bpz)3][PF6]2</t>
         </is>
       </c>
+      <c r="D8" s="10" t="n">
+        <v>450</v>
+      </c>
       <c r="E8" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="F8" s="10" t="n">
         <v>600</v>
       </c>
+      <c r="G8" s="10" t="n">
+        <v>626.38</v>
+      </c>
       <c r="H8" s="10" t="n">
-        <v>626.38</v>
-      </c>
-      <c r="I8" s="10" t="n">
         <v>1.82806</v>
       </c>
-      <c r="J8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Ir(dF(Me)ppy)3</t>
         </is>
       </c>
+      <c r="D9" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E9" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F9" s="10" t="n">
         <v>475</v>
       </c>
+      <c r="G9" s="10" t="n">
+        <v>2314.85</v>
+      </c>
       <c r="H9" s="10" t="n">
-        <v>2314.85</v>
-      </c>
-      <c r="I9" s="10" t="n">
         <v>4.73231</v>
       </c>
-      <c r="J9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(CF3)ppy)2(d(5,5)CF3bpy)]PF6</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E10" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F10" s="10" t="n">
         <v>620</v>
       </c>
+      <c r="G10" s="10" t="n">
+        <v>74.6559</v>
+      </c>
       <c r="H10" s="10" t="n">
-        <v>74.6559</v>
-      </c>
-      <c r="I10" s="10" t="n">
         <v>0.206387</v>
       </c>
-      <c r="J10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>[Ir(dFppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D11" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E11" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F11" s="10" t="n">
         <v>510</v>
       </c>
+      <c r="G11" s="10" t="n">
+        <v>1331.42</v>
+      </c>
       <c r="H11" s="10" t="n">
-        <v>1331.42</v>
-      </c>
-      <c r="I11" s="10" t="n">
         <v>3.82431</v>
       </c>
-      <c r="J11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(Me)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D12" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E12" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F12" s="10" t="n">
         <v>580</v>
       </c>
+      <c r="G12" s="10" t="n">
+        <v>1429.83</v>
+      </c>
       <c r="H12" s="10" t="n">
-        <v>1429.83</v>
-      </c>
-      <c r="I12" s="10" t="n">
         <v>3.903</v>
       </c>
-      <c r="J12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(CF3)ppy)2(bpy)]PF6</t>
         </is>
       </c>
+      <c r="D13" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E13" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F13" s="10" t="n">
         <v>475</v>
       </c>
+      <c r="G13" s="10" t="n">
+        <v>2335.66</v>
+      </c>
       <c r="H13" s="10" t="n">
-        <v>2335.66</v>
-      </c>
-      <c r="I13" s="10" t="n">
         <v>5.07795</v>
       </c>
-      <c r="J13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(Me)ppy)2(d(5,5)CH3bpy)]PF6</t>
         </is>
       </c>
+      <c r="D14" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E14" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F14" s="10" t="n">
         <v>500</v>
       </c>
+      <c r="G14" s="10" t="n">
+        <v>2330.54</v>
+      </c>
       <c r="H14" s="10" t="n">
-        <v>2330.54</v>
-      </c>
-      <c r="I14" s="10" t="n">
         <v>4.93813</v>
       </c>
-      <c r="J14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>[Ir(tCF3ppy)2(d(5,5)CH3bpy)]PF6</t>
         </is>
       </c>
+      <c r="D15" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E15" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F15" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G15" s="10" t="n">
+        <v>3417.56</v>
+      </c>
       <c r="H15" s="10" t="n">
-        <v>3417.56</v>
-      </c>
-      <c r="I15" s="10" t="n">
         <v>9.249000000000001</v>
       </c>
-      <c r="J15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(Me)ppy)2(d(OMe)bpy)]PF6</t>
         </is>
       </c>
+      <c r="D16" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E16" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F16" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G16" s="10" t="n">
+        <v>1539.96</v>
+      </c>
       <c r="H16" s="10" t="n">
-        <v>1539.96</v>
-      </c>
-      <c r="I16" s="10" t="n">
         <v>4.11826</v>
       </c>
-      <c r="J16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>[Ir(ppy)2(d(OMe)bpy)]PF6</t>
         </is>
       </c>
+      <c r="D17" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E17" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F17" s="10" t="n">
         <v>580</v>
       </c>
+      <c r="G17" s="10" t="n">
+        <v>277.386</v>
+      </c>
       <c r="H17" s="10" t="n">
-        <v>277.386</v>
-      </c>
-      <c r="I17" s="10" t="n">
         <v>0.916385</v>
       </c>
-      <c r="J17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>[Ir(tCF3ppy)2(d(5,5)OMebpy)]PF6</t>
         </is>
       </c>
+      <c r="D18" s="10" t="n">
+        <v>450</v>
+      </c>
       <c r="E18" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="F18" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G18" s="10" t="n">
+        <v>3664.57</v>
+      </c>
       <c r="H18" s="10" t="n">
-        <v>3664.57</v>
-      </c>
-      <c r="I18" s="10" t="n">
         <v>9.456340000000001</v>
       </c>
-      <c r="J18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>[Ir(dCF3ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D19" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E19" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F19" s="10" t="n">
         <v>500</v>
       </c>
+      <c r="G19" s="10" t="n">
+        <v>4755.86</v>
+      </c>
       <c r="H19" s="10" t="n">
-        <v>4755.86</v>
-      </c>
-      <c r="I19" s="10" t="n">
         <v>13.4651</v>
       </c>
-      <c r="J19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(6-OMe)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D20" s="10" t="n">
+        <v>405</v>
+      </c>
       <c r="E20" s="10" t="n">
-        <v>405</v>
-      </c>
-      <c r="F20" s="10" t="n">
         <v>495</v>
       </c>
+      <c r="G20" s="10" t="n">
+        <v>1519.18</v>
+      </c>
       <c r="H20" s="10" t="n">
-        <v>1519.18</v>
-      </c>
-      <c r="I20" s="10" t="n">
         <v>4.09436</v>
       </c>
-      <c r="J20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(OMe)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D21" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E21" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F21" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G21" s="10" t="n">
+        <v>1999.34</v>
+      </c>
       <c r="H21" s="10" t="n">
-        <v>1999.34</v>
-      </c>
-      <c r="I21" s="10" t="n">
         <v>4.45561</v>
       </c>
-      <c r="J21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>[Ir(tCF3ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D22" s="10" t="n">
+        <v>450</v>
+      </c>
       <c r="E22" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="F22" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G22" s="10" t="n">
+        <v>3304.66</v>
+      </c>
       <c r="H22" s="10" t="n">
-        <v>3304.66</v>
-      </c>
-      <c r="I22" s="10" t="n">
         <v>9.446070000000001</v>
       </c>
-      <c r="J22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>[Ir(tetraFppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D23" s="10" t="n">
+        <v>405</v>
+      </c>
       <c r="E23" s="10" t="n">
-        <v>405</v>
-      </c>
-      <c r="F23" s="10" t="n">
         <v>495</v>
       </c>
+      <c r="G23" s="10" t="n">
+        <v>4487.75</v>
+      </c>
       <c r="H23" s="10" t="n">
-        <v>4487.75</v>
-      </c>
-      <c r="I23" s="10" t="n">
         <v>10.683</v>
       </c>
-      <c r="J23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>[Ir(d(OMe)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D24" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E24" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F24" s="10" t="n">
         <v>490</v>
       </c>
+      <c r="G24" s="10" t="n">
+        <v>1334.3</v>
+      </c>
       <c r="H24" s="10" t="n">
-        <v>1334.3</v>
-      </c>
-      <c r="I24" s="10" t="n">
         <v>7.49855</v>
       </c>
-      <c r="J24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>[Ir(dF(4-Me)ppy)2(dtbbpy)]PF6</t>
         </is>
       </c>
+      <c r="D25" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E25" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F25" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G25" s="10" t="n">
+        <v>1314.69</v>
+      </c>
       <c r="H25" s="10" t="n">
-        <v>1314.69</v>
-      </c>
-      <c r="I25" s="10" t="n">
         <v>3.76114</v>
       </c>
-      <c r="J25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>[Ir(ppy)2(phen)]PF6</t>
         </is>
       </c>
+      <c r="D26" s="10" t="n">
+        <v>425</v>
+      </c>
       <c r="E26" s="10" t="n">
-        <v>425</v>
-      </c>
-      <c r="F26" s="10" t="n">
         <v>520</v>
       </c>
+      <c r="G26" s="10" t="n">
+        <v>763.793</v>
+      </c>
       <c r="H26" s="10" t="n">
-        <v>763.793</v>
-      </c>
-      <c r="I26" s="10" t="n">
         <v>2.06671</v>
       </c>
-      <c r="J26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>[Ir(CF3-pmb)3]</t>
         </is>
       </c>
+      <c r="D27" s="10" t="n">
+        <v>380</v>
+      </c>
       <c r="E27" s="10" t="n">
-        <v>380</v>
-      </c>
-      <c r="F27" s="10" t="n">
         <v>415</v>
       </c>
+      <c r="G27" s="10" t="n">
+        <v>6438.81</v>
+      </c>
       <c r="H27" s="10" t="n">
-        <v>6438.81</v>
-      </c>
-      <c r="I27" s="10" t="n">
         <v>14.9412</v>
       </c>
-      <c r="J27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>[Ir(CH3-pmb)3]</t>
         </is>
       </c>
+      <c r="D28" s="10" t="n">
+        <v>380</v>
+      </c>
       <c r="E28" s="10" t="n">
-        <v>380</v>
-      </c>
-      <c r="F28" s="10" t="n">
         <v>415</v>
       </c>
+      <c r="G28" s="10" t="n">
+        <v>2726.2</v>
+      </c>
       <c r="H28" s="10" t="n">
-        <v>2726.2</v>
-      </c>
-      <c r="I28" s="10" t="n">
         <v>8.609540000000001</v>
       </c>
-      <c r="J28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>[Ir(pmb)3]</t>
         </is>
       </c>
+      <c r="D29" s="10" t="n">
+        <v>380</v>
+      </c>
       <c r="E29" s="10" t="n">
-        <v>380</v>
-      </c>
-      <c r="F29" s="10" t="n">
         <v>415</v>
       </c>
+      <c r="G29" s="10" t="n">
+        <v>1620.59</v>
+      </c>
       <c r="H29" s="10" t="n">
-        <v>1620.59</v>
-      </c>
-      <c r="I29" s="10" t="n">
         <v>4.24662</v>
       </c>
-      <c r="J29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1273,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1324,7 +1236,7 @@
       <c r="C2" s="12" t="inlineStr"/>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>PC number used downstream and in the paper, 1-27.</t>
+          <t>PC number, 1-27.</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -1341,41 +1253,45 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>old_id</t>
+          <t>compound</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr"/>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>PC number during the screen, used by the raw files.</t>
+          <t>Compound.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>compound_identification.xlsx: Photocatalysts/old_id</t>
+          <t>compound_identification.xlsx: Photocatalysts/name</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Stern-Volmer screen</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>compound</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr"/>
+          <t>excitation / nm</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Compound.</t>
+          <t>Excitation filter centre in the Stern-Volmer screen, from the plate export (PC1 and PC3: from the photocatalyst sheet).</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>compound_identification.xlsx: Photocatalysts/name</t>
+          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: excitation_nm</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1303,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>excitation / nm</t>
+          <t>emission / nm</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1397,39 +1313,39 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Excitation filter centre in the Stern-Volmer screen, from the plate export (old PC1 and PC3: from the photocatalyst sheet).</t>
+          <t>Emission filter centre in the Stern-Volmer screen, from the plate export (PC1 and PC3: from the photocatalyst sheet).</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: excitation_nm</t>
+          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: emission_nm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Stern-Volmer screen</t>
+          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>emission / nm</t>
+          <t>tau0 / ns</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Emission filter centre in the Stern-Volmer screen, from the plate export (old PC1 and PC3: from the photocatalyst sheet).</t>
+          <t>Unquenched lifetime, single-exponential fit of the TCSPC trace.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: emission_nm</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_ns</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1357,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>tau0 / ns</t>
+          <t>tau0_err / ns</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1451,12 +1367,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Unquenched lifetime, single-exponential fit of pc_tcspc/PC&lt;n&gt;.txt.</t>
+          <t>Standard error of that fit.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_ns</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_err_ns</t>
         </is>
       </c>
     </row>
@@ -1468,50 +1384,34 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>tau0_err / ns</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
+          <t>tau0_note</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr"/>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Standard error of that fit.</t>
+          <t>Deviation from the standard fit window.</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_err_ns</t>
+          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: note</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Excited-state lifetime, TCSPC in MeCN under Ar</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>tau0_note</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Deviation from the standard fit window.</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: note</t>
-        </is>
-      </c>
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>One row per photocatalyst in the screen, sorted by new_id. PC22 is kept here and</t>
+        </is>
+      </c>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="13" t="n"/>
@@ -1520,7 +1420,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>One row per photocatalyst in the screen, sorted by new_id. The raw files use old_id;</t>
+          <t>excluded by the theory benchmark (see SI).</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -1531,7 +1431,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>the mapping is data/compound_identification.xlsx. new_id 22 (old 24) is kept here and dropped</t>
+          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -1539,28 +1439,6 @@
       <c r="D12" s="13" t="n"/>
       <c r="E12" s="12" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>by the theory benchmark: its emission was too weak.</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Read with pandas as: pd.read_excel(path, header=1), then drop the 'Unnamed' columns.</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
+++ b/data/experimental_data_processed/photocatalyst_properties_exp.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: excitation_nm</t>
+          <t>experimental_data_processed/plate_reader_filters.csv: excitation_nm</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/stern_volmer/plate_reader_filters.csv: emission_nm</t>
+          <t>experimental_data_processed/plate_reader_filters.csv: emission_nm</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_ns</t>
+          <t>experimental_data_processed/lifetimes_tcspc.csv: tau0_ns</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: tau0_err_ns</t>
+          <t>experimental_data_processed/lifetimes_tcspc.csv: tau0_err_ns</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>experimental_data_raw/pc_tcspc/lifetimes_tcspc.csv: note</t>
+          <t>experimental_data_processed/lifetimes_tcspc.csv: note</t>
         </is>
       </c>
     </row>
